--- a/progress.xlsx
+++ b/progress.xlsx
@@ -5,20 +5,31 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\work_education\Data Science\leectode\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\programming\leectode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF73BEB8-B758-4162-A2A2-7BC8D129F2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98B8FB7-0CE7-46D0-921B-CAC89A2BC9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2263" yWindow="2263" windowWidth="24686" windowHeight="13054" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -57,19 +68,22 @@
     <t>Revisit</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>array</t>
   </si>
   <si>
     <t>easy</t>
   </si>
   <si>
-    <t>sliding_window</t>
-  </si>
-  <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>two sum</t>
+  </si>
+  <si>
+    <t>hashmap</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -158,6 +172,27 @@
         <charset val="204"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -221,27 +256,6 @@
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -329,26 +343,26 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -379,7 +393,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I3" totalsRowShown="0" headerRowDxfId="9" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I3" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:I3" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{685A81AA-CE5A-4907-AA51-69C7AEC5D23E}" name="ID" dataDxfId="8"/>
@@ -387,10 +401,12 @@
     <tableColumn id="3" xr3:uid="{DE3E6F2D-9ED0-4FE0-B395-2F1D92CA3F31}" name="Topic" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{7EC57E03-7F69-4E60-A2F1-84516852D8E5}" name="Difficulty" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{8D20F692-0FDA-4823-8437-5AE39FF2F9E0}" name="Pattern" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{E31E146C-4BC8-413A-AD68-F6E7CD61AA35}" name="Date solved" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{A24300F8-929F-4534-AA9D-367561867519}" name="Solved alone" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{B1749158-4C0E-47C1-9D16-C8E9F860B220}" name="Time (min)" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{8858FB64-F39C-4C0F-B666-C34458EA675D}" name="Revisit" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{E31E146C-4BC8-413A-AD68-F6E7CD61AA35}" name="Date solved" dataDxfId="0">
+      <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{A24300F8-929F-4534-AA9D-367561867519}" name="Solved alone" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{B1749158-4C0E-47C1-9D16-C8E9F860B220}" name="Time (min)" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{8858FB64-F39C-4C0F-B666-C34458EA675D}" name="Revisit" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -706,31 +722,31 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46155</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4">
-        <v>46023</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\programming\leectode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98B8FB7-0CE7-46D0-921B-CAC89A2BC9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB50679-E594-4B2B-9321-AFDC4909401A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2263" yWindow="2263" windowWidth="24686" windowHeight="13054" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32829" yWindow="-9" windowWidth="16628" windowHeight="8983" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -84,6 +84,27 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>check if array is good</t>
+  </si>
+  <si>
+    <t>contains duplicate</t>
+  </si>
+  <si>
+    <t>valid anagram</t>
+  </si>
+  <si>
+    <t>hashtable</t>
+  </si>
+  <si>
+    <t>group anagrams</t>
+  </si>
+  <si>
+    <t>hasmap, sorting</t>
+  </si>
+  <si>
+    <t>hint</t>
   </si>
 </sst>
 </file>
@@ -172,27 +193,6 @@
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -236,6 +236,27 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -393,20 +414,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I3" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I3" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I6" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{685A81AA-CE5A-4907-AA51-69C7AEC5D23E}" name="ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{A1ED6610-48F4-46DD-99A2-0C3D0643BFAF}" name="Problem" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{DE3E6F2D-9ED0-4FE0-B395-2F1D92CA3F31}" name="Topic" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{7EC57E03-7F69-4E60-A2F1-84516852D8E5}" name="Difficulty" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{8D20F692-0FDA-4823-8437-5AE39FF2F9E0}" name="Pattern" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{E31E146C-4BC8-413A-AD68-F6E7CD61AA35}" name="Date solved" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{E31E146C-4BC8-413A-AD68-F6E7CD61AA35}" name="Date solved" dataDxfId="3">
       <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A24300F8-929F-4534-AA9D-367561867519}" name="Solved alone" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{B1749158-4C0E-47C1-9D16-C8E9F860B220}" name="Time (min)" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{8858FB64-F39C-4C0F-B666-C34458EA675D}" name="Revisit" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{A24300F8-929F-4534-AA9D-367561867519}" name="Solved alone" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{B1749158-4C0E-47C1-9D16-C8E9F860B220}" name="Time (min)" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{8858FB64-F39C-4C0F-B666-C34458EA675D}" name="Revisit" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -675,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.61328125" style="2" bestFit="1" customWidth="1"/>
@@ -734,7 +755,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F2" s="4">
         <v>46155</v>
@@ -750,25 +771,133 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="3"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="7"/>
+      <c r="A3" s="3">
+        <v>2784</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46156</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>217</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="4">
+        <f ca="1">TODAY()</f>
+        <v>46156</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="5">
+        <v>5</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>242</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4">
+        <f ca="1">TODAY()</f>
+        <v>46156</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>49</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4">
+        <f ca="1">TODAY()</f>
+        <v>46156</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="5">
+        <v>10</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D6" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G3" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G6" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
       <formula1>"yes,hint,solution"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I3" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I6" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\programming\leectode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB50679-E594-4B2B-9321-AFDC4909401A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369B14BE-3F0A-4537-A47D-872997909C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32829" yWindow="-9" windowWidth="16628" windowHeight="8983" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="10440" windowWidth="26010" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -105,6 +105,27 @@
   </si>
   <si>
     <t>hint</t>
+  </si>
+  <si>
+    <t>find minimum in rotated sorted array</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>two pointers</t>
+  </si>
+  <si>
+    <t>top k frequent elements</t>
+  </si>
+  <si>
+    <t>hashmap, sorting</t>
+  </si>
+  <si>
+    <t>product of array except self</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -414,8 +435,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I6" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I9" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I9" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{685A81AA-CE5A-4907-AA51-69C7AEC5D23E}" name="ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{A1ED6610-48F4-46DD-99A2-0C3D0643BFAF}" name="Problem" dataDxfId="7"/>
@@ -696,23 +717,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.61328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.3046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.23046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.53515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.23046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.07421875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.23046875" style="2"/>
+    <col min="1" max="1" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -741,7 +761,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -770,7 +790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2784</v>
       </c>
@@ -799,7 +819,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>217</v>
       </c>
@@ -816,7 +836,6 @@
         <v>18</v>
       </c>
       <c r="F4" s="4">
-        <f ca="1">TODAY()</f>
         <v>46156</v>
       </c>
       <c r="G4" s="7" t="s">
@@ -829,7 +848,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>242</v>
       </c>
@@ -846,7 +865,6 @@
         <v>13</v>
       </c>
       <c r="F5" s="4">
-        <f ca="1">TODAY()</f>
         <v>46156</v>
       </c>
       <c r="G5" s="7" t="s">
@@ -859,7 +877,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>49</v>
       </c>
@@ -870,13 +888,12 @@
         <v>9</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="4">
-        <f ca="1">TODAY()</f>
         <v>46156</v>
       </c>
       <c r="G6" s="7" t="s">
@@ -886,18 +903,108 @@
         <v>10</v>
       </c>
       <c r="I6" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>153</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="4">
+        <f ca="1">TODAY()</f>
+        <v>46157</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="5">
+        <v>15</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>347</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="4">
+        <f ca="1">TODAY()</f>
+        <v>46157</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="5">
+        <v>15</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>238</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="4">
+        <f ca="1">TODAY()</f>
+        <v>46157</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="5">
+        <v>20</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D6" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D9" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G6" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G9" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
       <formula1>"yes,hint,solution"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I6" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I9" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\programming\leectode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369B14BE-3F0A-4537-A47D-872997909C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0757C3-4ACD-4B4C-919B-6823E6DF991E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="10440" windowWidth="26010" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5085" yWindow="5010" windowWidth="38700" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>valid sudoku</t>
+  </si>
+  <si>
+    <t>longest consecutive sequence</t>
+  </si>
+  <si>
+    <t>solution</t>
   </si>
 </sst>
 </file>
@@ -176,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -191,6 +200,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -214,28 +224,7 @@
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -277,7 +266,7 @@
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -299,6 +288,27 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -435,20 +445,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I9" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I9" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I12" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I12" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{685A81AA-CE5A-4907-AA51-69C7AEC5D23E}" name="ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{A1ED6610-48F4-46DD-99A2-0C3D0643BFAF}" name="Problem" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{DE3E6F2D-9ED0-4FE0-B395-2F1D92CA3F31}" name="Topic" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{7EC57E03-7F69-4E60-A2F1-84516852D8E5}" name="Difficulty" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{8D20F692-0FDA-4823-8437-5AE39FF2F9E0}" name="Pattern" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{E31E146C-4BC8-413A-AD68-F6E7CD61AA35}" name="Date solved" dataDxfId="3">
-      <calculatedColumnFormula>TODAY()</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{A24300F8-929F-4534-AA9D-367561867519}" name="Solved alone" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{B1749158-4C0E-47C1-9D16-C8E9F860B220}" name="Time (min)" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{8858FB64-F39C-4C0F-B666-C34458EA675D}" name="Revisit" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{8D20F692-0FDA-4823-8437-5AE39FF2F9E0}" name="Pattern" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{55620A32-9382-46D3-8462-A6C66059DA4A}" name="Date solved" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{A24300F8-929F-4534-AA9D-367561867519}" name="Solved alone" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{B1749158-4C0E-47C1-9D16-C8E9F860B220}" name="Time (min)" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{8858FB64-F39C-4C0F-B666-C34458EA675D}" name="Revisit" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -717,22 +725,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.28515625" style="2"/>
+    <col min="11" max="11" width="9.28515625" style="2"/>
+    <col min="12" max="12" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -761,7 +772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -789,8 +800,9 @@
       <c r="I2" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2784</v>
       </c>
@@ -818,8 +830,9 @@
       <c r="I3" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>217</v>
       </c>
@@ -847,8 +860,9 @@
       <c r="I4" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>242</v>
       </c>
@@ -876,8 +890,9 @@
       <c r="I5" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>49</v>
       </c>
@@ -905,8 +920,9 @@
       <c r="I6" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>153</v>
       </c>
@@ -923,7 +939,6 @@
         <v>24</v>
       </c>
       <c r="F7" s="4">
-        <f ca="1">TODAY()</f>
         <v>46157</v>
       </c>
       <c r="G7" s="7" t="s">
@@ -935,8 +950,9 @@
       <c r="I7" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>347</v>
       </c>
@@ -953,7 +969,6 @@
         <v>26</v>
       </c>
       <c r="F8" s="4">
-        <f ca="1">TODAY()</f>
         <v>46157</v>
       </c>
       <c r="G8" s="7" t="s">
@@ -965,8 +980,9 @@
       <c r="I8" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>238</v>
       </c>
@@ -983,7 +999,6 @@
         <v>28</v>
       </c>
       <c r="F9" s="4">
-        <f ca="1">TODAY()</f>
         <v>46157</v>
       </c>
       <c r="G9" s="7" t="s">
@@ -995,22 +1010,95 @@
       <c r="I9" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="L9" s="8"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>36</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="4">
+        <v>46160</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="5">
+        <v>15</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>128</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46160</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="5">
+        <v>60</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="8"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D9" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D12" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G9" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G12" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
       <formula1>"yes,hint,solution"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I9" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I12" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\programming\leectode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0757C3-4ACD-4B4C-919B-6823E6DF991E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AA0BB9-2CFE-4A55-A4F2-3DD804A02FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5085" yWindow="5010" windowWidth="38700" windowHeight="15240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32811" yWindow="-111" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -135,6 +135,21 @@
   </si>
   <si>
     <t>solution</t>
+  </si>
+  <si>
+    <t>valid parantheses</t>
+  </si>
+  <si>
+    <t>stack</t>
+  </si>
+  <si>
+    <t>min stack</t>
+  </si>
+  <si>
+    <t>evaluate reverse polish notation</t>
+  </si>
+  <si>
+    <t>daily temperatures</t>
   </si>
 </sst>
 </file>
@@ -224,7 +239,28 @@
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -266,7 +302,7 @@
         <charset val="204"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -288,27 +324,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -445,18 +460,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I12" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I12" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I15" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I15" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{685A81AA-CE5A-4907-AA51-69C7AEC5D23E}" name="ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{A1ED6610-48F4-46DD-99A2-0C3D0643BFAF}" name="Problem" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{DE3E6F2D-9ED0-4FE0-B395-2F1D92CA3F31}" name="Topic" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{7EC57E03-7F69-4E60-A2F1-84516852D8E5}" name="Difficulty" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{8D20F692-0FDA-4823-8437-5AE39FF2F9E0}" name="Pattern" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{55620A32-9382-46D3-8462-A6C66059DA4A}" name="Date solved" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{A24300F8-929F-4534-AA9D-367561867519}" name="Solved alone" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{B1749158-4C0E-47C1-9D16-C8E9F860B220}" name="Time (min)" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{8858FB64-F39C-4C0F-B666-C34458EA675D}" name="Revisit" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{8D20F692-0FDA-4823-8437-5AE39FF2F9E0}" name="Pattern" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{55620A32-9382-46D3-8462-A6C66059DA4A}" name="Date solved" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{A24300F8-929F-4534-AA9D-367561867519}" name="Solved alone" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{B1749158-4C0E-47C1-9D16-C8E9F860B220}" name="Time (min)" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{8858FB64-F39C-4C0F-B666-C34458EA675D}" name="Revisit" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -725,25 +740,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.28515625" style="2"/>
-    <col min="12" max="12" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.28515625" style="2"/>
+    <col min="1" max="1" width="7.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.69140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.84375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.3046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.3046875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.3046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.3046875" style="2"/>
+    <col min="12" max="12" width="12.69140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.3046875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -772,7 +787,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -802,7 +817,7 @@
       </c>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2784</v>
       </c>
@@ -832,7 +847,7 @@
       </c>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>217</v>
       </c>
@@ -862,7 +877,7 @@
       </c>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>242</v>
       </c>
@@ -892,7 +907,7 @@
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>49</v>
       </c>
@@ -922,7 +937,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>153</v>
       </c>
@@ -952,7 +967,7 @@
       </c>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>347</v>
       </c>
@@ -982,7 +997,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>238</v>
       </c>
@@ -1012,7 +1027,7 @@
       </c>
       <c r="L9" s="8"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>36</v>
       </c>
@@ -1042,7 +1057,7 @@
       </c>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>128</v>
       </c>
@@ -1072,26 +1087,131 @@
       </c>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="7"/>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>20</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46175</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="5">
+        <v>10</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>155</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="4">
+        <v>46175</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="5">
+        <v>20</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>150</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46175</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="5">
+        <v>10</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>739</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46175</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="5">
+        <v>20</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D12" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D15" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G12" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G15" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
       <formula1>"yes,hint,solution"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I12" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I15" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\programming\leectode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AA0BB9-2CFE-4A55-A4F2-3DD804A02FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB49415-6B76-42E3-A295-F18EAC492540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32811" yWindow="-111" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-86" yWindow="514" windowWidth="33086" windowHeight="17366" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="38">
   <si>
     <t>ID</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>daily temperatures</t>
+  </si>
+  <si>
+    <t>car fleet</t>
   </si>
 </sst>
 </file>
@@ -460,8 +463,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I15" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I15" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I16" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I16" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{685A81AA-CE5A-4907-AA51-69C7AEC5D23E}" name="ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{A1ED6610-48F4-46DD-99A2-0C3D0643BFAF}" name="Problem" dataDxfId="7"/>
@@ -740,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.53515625" style="2" bestFit="1" customWidth="1"/>
@@ -1203,15 +1206,44 @@
         <v>14</v>
       </c>
     </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>853</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="4">
+        <v>46176</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="5">
+        <v>25</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D15" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D16" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G15" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G16" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
       <formula1>"yes,hint,solution"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I15" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I16" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\programming\leectode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB49415-6B76-42E3-A295-F18EAC492540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AAC56A-90CD-46BD-9641-AE151BD645FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="514" windowWidth="33086" windowHeight="17366" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>car fleet</t>
+  </si>
+  <si>
+    <t>valid palindrome</t>
+  </si>
+  <si>
+    <t>two sum ii - input array is sorted</t>
   </si>
 </sst>
 </file>
@@ -463,8 +469,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I16" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I16" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I19" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I19" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{685A81AA-CE5A-4907-AA51-69C7AEC5D23E}" name="ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{A1ED6610-48F4-46DD-99A2-0C3D0643BFAF}" name="Problem" dataDxfId="7"/>
@@ -743,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.53515625" style="2" bestFit="1" customWidth="1"/>
@@ -1235,15 +1241,84 @@
         <v>14</v>
       </c>
     </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>125</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="4">
+        <v>46181</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="5">
+        <v>10</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>167</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="4">
+        <v>46181</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="5">
+        <v>20</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="7"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D16" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D19" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G16" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G19" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
       <formula1>"yes,hint,solution"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I16" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I19" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\programming\leectode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AAC56A-90CD-46BD-9641-AE151BD645FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC75F25-1515-4132-98C0-C25414877BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-86" yWindow="0" windowWidth="16629" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -159,6 +159,15 @@
   </si>
   <si>
     <t>two sum ii - input array is sorted</t>
+  </si>
+  <si>
+    <t>3Sum</t>
+  </si>
+  <si>
+    <t>Reverse Linked List</t>
+  </si>
+  <si>
+    <t>linked list</t>
   </si>
 </sst>
 </file>
@@ -469,8 +478,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I19" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I19" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I20" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I20" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{685A81AA-CE5A-4907-AA51-69C7AEC5D23E}" name="ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{A1ED6610-48F4-46DD-99A2-0C3D0643BFAF}" name="Problem" dataDxfId="7"/>
@@ -749,13 +758,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.53515625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.69140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.84375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.3046875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.3046875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.3046875" style="2" customWidth="1"/>
     <col min="7" max="7" width="16.53515625" style="2" bestFit="1" customWidth="1"/>
@@ -1300,25 +1308,72 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="3"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="7"/>
+      <c r="A19" s="3">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46188</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="5">
+        <v>60</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>206</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="4">
+        <v>46188</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="5">
+        <v>5</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D19" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D20" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G19" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G20" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
       <formula1>"yes,hint,solution"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I19" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I20" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\programming\leectode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC75F25-1515-4132-98C0-C25414877BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D80460B-BCF1-42FF-BE41-B3DDB0C3A427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="0" windowWidth="16629" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="45">
   <si>
     <t>ID</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>linked list</t>
+  </si>
+  <si>
+    <t>merge two sorted lists</t>
+  </si>
+  <si>
+    <t>linked list cycle</t>
   </si>
 </sst>
 </file>
@@ -478,8 +484,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I20" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I20" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I22" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I22" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{685A81AA-CE5A-4907-AA51-69C7AEC5D23E}" name="ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{A1ED6610-48F4-46DD-99A2-0C3D0643BFAF}" name="Problem" dataDxfId="7"/>
@@ -758,24 +764,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.53515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.69140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.3046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.3046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.3046875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.53515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.3046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.15234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.3046875" style="2"/>
-    <col min="12" max="12" width="12.69140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.3046875" style="2"/>
+    <col min="1" max="1" width="7.53125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.53125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" style="2"/>
+    <col min="12" max="12" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,7 +810,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -834,7 +840,7 @@
       </c>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>2784</v>
       </c>
@@ -864,7 +870,7 @@
       </c>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>217</v>
       </c>
@@ -894,7 +900,7 @@
       </c>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>242</v>
       </c>
@@ -924,7 +930,7 @@
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>49</v>
       </c>
@@ -954,7 +960,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>153</v>
       </c>
@@ -984,7 +990,7 @@
       </c>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>347</v>
       </c>
@@ -1014,7 +1020,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <v>238</v>
       </c>
@@ -1044,7 +1050,7 @@
       </c>
       <c r="L9" s="8"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
         <v>36</v>
       </c>
@@ -1074,7 +1080,7 @@
       </c>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
         <v>128</v>
       </c>
@@ -1104,7 +1110,7 @@
       </c>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
         <v>20</v>
       </c>
@@ -1133,7 +1139,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
         <v>155</v>
       </c>
@@ -1162,7 +1168,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <v>150</v>
       </c>
@@ -1191,7 +1197,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <v>739</v>
       </c>
@@ -1220,7 +1226,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
         <v>853</v>
       </c>
@@ -1249,7 +1255,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>125</v>
       </c>
@@ -1278,7 +1284,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>167</v>
       </c>
@@ -1307,7 +1313,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>15</v>
       </c>
@@ -1336,7 +1342,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>206</v>
       </c>
@@ -1365,15 +1371,73 @@
         <v>14</v>
       </c>
     </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" s="3">
+        <v>21</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="4">
+        <v>46190</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="5">
+        <v>30</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" s="3">
+        <v>141</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="4">
+        <v>46190</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="5">
+        <v>10</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D20" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G20" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G22" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
       <formula1>"yes,hint,solution"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I20" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I22" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\programming\leectode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D80460B-BCF1-42FF-BE41-B3DDB0C3A427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5984F100-970F-4733-B721-C076CA769ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35520" yWindow="2597" windowWidth="24686" windowHeight="13054" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="48">
   <si>
     <t>ID</t>
   </si>
@@ -174,6 +174,15 @@
   </si>
   <si>
     <t>linked list cycle</t>
+  </si>
+  <si>
+    <t>reorder list</t>
+  </si>
+  <si>
+    <t>recursion</t>
+  </si>
+  <si>
+    <t>remove nth node from end of list</t>
   </si>
 </sst>
 </file>
@@ -484,8 +493,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I22" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I22" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}" name="Table1" displayName="Table1" ref="A1:I24" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I24" xr:uid="{3546B0E1-7CD8-414E-B94D-DE9006BAE699}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{685A81AA-CE5A-4907-AA51-69C7AEC5D23E}" name="ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{A1ED6610-48F4-46DD-99A2-0C3D0643BFAF}" name="Problem" dataDxfId="7"/>
@@ -764,24 +773,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.53125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.53125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.33203125" style="2"/>
-    <col min="12" max="12" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.33203125" style="2"/>
+    <col min="1" max="1" width="7.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.69140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.3046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.3046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.3046875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.3046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.3046875" style="2"/>
+    <col min="12" max="12" width="12.69140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.3046875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -810,7 +819,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -840,7 +849,7 @@
       </c>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2784</v>
       </c>
@@ -870,7 +879,7 @@
       </c>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>217</v>
       </c>
@@ -900,7 +909,7 @@
       </c>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>242</v>
       </c>
@@ -930,7 +939,7 @@
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>49</v>
       </c>
@@ -960,7 +969,7 @@
       </c>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>153</v>
       </c>
@@ -990,7 +999,7 @@
       </c>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>347</v>
       </c>
@@ -1020,7 +1029,7 @@
       </c>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>238</v>
       </c>
@@ -1050,7 +1059,7 @@
       </c>
       <c r="L9" s="8"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>36</v>
       </c>
@@ -1080,7 +1089,7 @@
       </c>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>128</v>
       </c>
@@ -1110,7 +1119,7 @@
       </c>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>20</v>
       </c>
@@ -1139,7 +1148,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>155</v>
       </c>
@@ -1168,7 +1177,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>150</v>
       </c>
@@ -1197,7 +1206,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>739</v>
       </c>
@@ -1226,7 +1235,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>853</v>
       </c>
@@ -1255,7 +1264,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>125</v>
       </c>
@@ -1284,7 +1293,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>167</v>
       </c>
@@ -1313,7 +1322,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>15</v>
       </c>
@@ -1342,7 +1351,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>206</v>
       </c>
@@ -1371,7 +1380,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>21</v>
       </c>
@@ -1400,7 +1409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>141</v>
       </c>
@@ -1429,15 +1438,73 @@
         <v>14</v>
       </c>
     </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
+        <v>143</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="4">
+        <v>46192</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="5">
+        <v>30</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="4">
+        <v>46192</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="5">
+        <v>15</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D24" xr:uid="{D69446B5-8747-44CE-BE89-153804E279E9}">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G22" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G24" xr:uid="{AA9FED16-AB59-4964-A640-7E052C0BDD09}">
       <formula1>"yes,hint,solution"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I22" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I24" xr:uid="{6F15E38E-73F1-4900-BC5B-F3374EB836CD}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
